--- a/src/main/resources/excel/员工月度计件工资导入模板.xlsx
+++ b/src/main/resources/excel/员工月度计件工资导入模板.xlsx
@@ -68,7 +68,7 @@
     <t>实发工资</t>
   </si>
   <si>
-    <t>海员1(小程序）</t>
+    <t>海员1</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1112,11 @@
       </c>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1"/>
+    <row r="3" ht="14.25" customHeight="1" spans="1:1">
+      <c r="A3" s="1">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入时间1900/1/1到2099/1/1" sqref="A$1:A$1048576">
